--- a/docs/StructureDefinition-BRAgendamentoRegulacaoAssistencial.xlsx
+++ b/docs/StructureDefinition-BRAgendamentoRegulacaoAssistencial.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5577" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5575" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -54,67 +54,67 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-04-04</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Ministério da Saúde do Brasil</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Appointment</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Appointment</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2023-04-04</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>Ministério da Saúde do Brasil</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>resource</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Appointment</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Appointment</t>
-  </si>
-  <si>
-    <t>Abstract</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -281,9 +281,6 @@
     <t>Appointment.id</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -303,6 +300,9 @@
     <t>Resource.id</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Appointment.meta</t>
   </si>
   <si>
@@ -496,10 +496,10 @@
     <t>Appointment.status</t>
   </si>
   <si>
-    <t>Status da solicitação.</t>
-  </si>
-  <si>
-    <t>O código que identifica unicamente o status da solicitação, conforme tabela de status de solicitação.</t>
+    <t>proposed | pending | booked | arrived | fulfilled | cancelled | noshow | entered-in-error | checked-in | waitlist</t>
+  </si>
+  <si>
+    <t>The overall status of the Appointment. Each of the participants has their own participation status which indicates their involvement in the process, however this status indicates the shared status.</t>
   </si>
   <si>
     <t>If the Appointment's status is "cancelled" then all participants are expected to have their calendars released for the appointment period, and as such any Slots that were marked as BUSY can be re-set to FREE.
@@ -509,10 +509,11 @@
     <t>required</t>
   </si>
   <si>
-    <t>Status do agendamento</t>
-  </si>
-  <si>
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRStatusAgendamentoRegulacaoAssistencial</t>
+  </si>
+  <si>
+    <t>mira-13
+mira-14mira-15mira-16mira-17mira-18mira-19</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -555,10 +556,10 @@
     <t>Appointment.serviceCategory</t>
   </si>
   <si>
-    <t>Modalidade assistencial.</t>
-  </si>
-  <si>
-    <t>O código que identifica unicamente a modalidade, conforme tabela de modalidades.</t>
+    <t>Modalidade assistencial</t>
+  </si>
+  <si>
+    <t>Modalidade assistencial que gerou a solicitação do procedimento.</t>
   </si>
   <si>
     <t>Modalidade Assistencial</t>
@@ -784,7 +785,7 @@
     <t>Appointment.serviceType</t>
   </si>
   <si>
-    <t>Código do procedimento.</t>
+    <t>Código do procedimento</t>
   </si>
   <si>
     <t>O código que identifica unicamente o procedimento conforme tabela SUS.</t>
@@ -838,10 +839,11 @@
     <t>Appointment.specialty</t>
   </si>
   <si>
-    <t>Identificador da especialidade médica do executante.</t>
-  </si>
-  <si>
-    <t>O código que identifica unicamente a especialidade do executante conforme tabela de CBO.</t>
+    <t>Especialidade médica do executante</t>
+  </si>
+  <si>
+    <t>Identificação da especialidade médica do profissional executante do procedimento, conforme tabela de CBO. 
+Caso o procedimento informado pertença à forma de organização 03.01.01 da tabela SUS, o código CBO será obrigatório.</t>
   </si>
   <si>
     <t>Classificação Brasileira de Ocupações.</t>
@@ -892,10 +894,10 @@
     <t>Appointment.appointmentType</t>
   </si>
   <si>
-    <t>Caráter da solicitação.</t>
-  </si>
-  <si>
-    <t>O código que identifica unicamente o caráter da solicitação, conforme tabela de caráter da solicitação.</t>
+    <t>Caráter da solicitação</t>
+  </si>
+  <si>
+    <t>O código que identifica unicamente o caráter da solicitação do procedimento, conforme tabela de caráter da solicitação.</t>
   </si>
   <si>
     <t>Caráter de atendimento.</t>
@@ -973,14 +975,14 @@
     <t>Appointment.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/BRCID10Avaliado-1.0)
+    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/BRProblemaDiagnostico)
 </t>
   </si>
   <si>
     <t>Motivo da solicitação</t>
   </si>
   <si>
-    <t>Reason the appointment has been scheduled to take place, as specified using information from another resource. When the patient arrives and the encounter begins it may be used as the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
+    <t>Identificação do motivo da solicitação do procedimento, conforme Classificação Internacional de Doenças - CID ou Classificação Internacional de Atenção Primária - CIAP.</t>
   </si>
   <si>
     <t>Request.reasonReference</t>
@@ -1334,7 +1336,10 @@
     <t>regulatoryOrganization</t>
   </si>
   <si>
-    <t>Estabelecimento de Saúde Regulador</t>
+    <t>Estabelecimento de saúde regulador</t>
+  </si>
+  <si>
+    <t>Identificação única do estabelecimento regulador, por meio do CNES.</t>
   </si>
   <si>
     <t>Appointment.supportingInformation:regulatoryOrganization.id</t>
@@ -1350,6 +1355,10 @@
   </si>
   <si>
     <t>Appointment.supportingInformation:regulatoryOrganization.identifier</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+estab-2:O número do CNES do estabelecimento de saúde é inválido (identifier.value). O número deve conter 7 dígitos e não pode conter letras ou caracteres especiais, apenas números. {value.matches('^(?!(\\d)\\1{6})\\d{7}$')}</t>
   </si>
   <si>
     <t>Appointment.supportingInformation:regulatoryOrganization.identifier.id</t>
@@ -1389,10 +1398,14 @@
 </t>
   </si>
   <si>
-    <t>Data Inicial de Agendamento</t>
-  </si>
-  <si>
-    <t>A data e hora inicial em que o procedimento regulado foi agendado no padrão ISO 8601.</t>
+    <t>Data de agendamento - início</t>
+  </si>
+  <si>
+    <t>A data e hora agendada para a realização do procedimento regulado no padrão ISO 8601.</t>
+  </si>
+  <si>
+    <t>mira-2
+mira-5mira-7mira-10</t>
   </si>
   <si>
     <t>Request.occurrence[x]</t>
@@ -1413,10 +1426,7 @@
     <t>Appointment.end</t>
   </si>
   <si>
-    <t>Data Final de Agendamento</t>
-  </si>
-  <si>
-    <t>A data e hora final em que o procedimento regulado foi agendado no padrão ISO 8601.</t>
+    <t>Data de agendamento - fim</t>
   </si>
   <si>
     <t>.effectiveTime.high</t>
@@ -1473,10 +1483,10 @@
 </t>
   </si>
   <si>
-    <t>Data da Autorização</t>
-  </si>
-  <si>
-    <t>A data e hora da autoriação do procedimento regulado no padrão ISO 8601.</t>
+    <t>Data de autorização</t>
+  </si>
+  <si>
+    <t>A data e hora em que a solicitação de procedimento regulado foi autorizada no padrão ISO 8601.</t>
   </si>
   <si>
     <t>This property is required for many use cases where the age of an appointment is considered in processing workflows for scheduling and billing of appointments.</t>
@@ -1574,10 +1584,10 @@
 </t>
   </si>
   <si>
-    <t>Paciente</t>
-  </si>
-  <si>
-    <t>List of participants involved in the appointment.</t>
+    <t>Identificador do paciente</t>
+  </si>
+  <si>
+    <t>Identificação única do paciente, por meio de CPF ou CNS.</t>
   </si>
   <si>
     <t>app-1:Either the type or actor on the participant SHALL be specified {type.exists() or actor.exists()}
@@ -1687,12 +1697,6 @@
 </t>
   </si>
   <si>
-    <t>Person, Location/HealthcareService or Device</t>
-  </si>
-  <si>
-    <t>A Person, Location/HealthcareService or Device that is participating in the appointment.</t>
-  </si>
-  <si>
     <t>performer.person | reusableDevice.manufacturedDevice | subject.patient | location.serviceDeliveryLocation</t>
   </si>
   <si>
@@ -1720,6 +1724,10 @@
     <t>Appointment.participant.actor.identifier</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ident-1:O número de CPF ou CNS informado é inválido (identifier.value). {value.matches('^(?!(\\d)\\1{10})\\d{11}$') or value.matches('^(?!(\\d)\\1{14})[125789]\\d{14}$')}</t>
+  </si>
+  <si>
     <t>Appointment.participant.actor.identifier.id</t>
   </si>
   <si>
@@ -1771,10 +1779,13 @@
     <t>Appointment.participant.status</t>
   </si>
   <si>
+    <t>Status da participação no agendamento</t>
+  </si>
+  <si>
+    <t>Participation status of the actor.</t>
+  </si>
+  <si>
     <t>Status da participação no agendamento.</t>
-  </si>
-  <si>
-    <t>Participation status of the actor.</t>
   </si>
   <si>
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRStatusParticipante</t>
@@ -2007,45 +2018,43 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>9</v>
@@ -2053,54 +2062,54 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2290,10 +2299,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2373,7 +2382,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>
@@ -2419,28 +2428,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2490,13 +2499,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2536,16 +2545,16 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>96</v>
@@ -2611,7 +2620,7 @@
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
@@ -2657,10 +2666,10 @@
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>102</v>
@@ -2728,7 +2737,7 @@
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -2845,7 +2854,7 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
@@ -2885,7 +2894,7 @@
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2962,7 +2971,7 @@
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
@@ -3242,7 +3251,7 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
@@ -3364,7 +3373,7 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>146</v>
@@ -3467,19 +3476,19 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G12" t="s" s="2">
+      <c r="J12" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>108</v>
@@ -3519,11 +3528,9 @@
       <c r="X12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3544,13 +3551,13 @@
         <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
@@ -3596,7 +3603,7 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>167</v>
@@ -3660,7 +3667,7 @@
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
@@ -3697,19 +3704,19 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J14" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>167</v>
@@ -3815,7 +3822,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3890,7 +3897,7 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
@@ -4044,19 +4051,19 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>192</v>
@@ -4166,7 +4173,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -4241,7 +4248,7 @@
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
@@ -4395,19 +4402,19 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>102</v>
@@ -4477,7 +4484,7 @@
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -4517,16 +4524,16 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>181</v>
@@ -4594,7 +4601,7 @@
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
@@ -4631,19 +4638,19 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>108</v>
@@ -4711,7 +4718,7 @@
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -4751,16 +4758,16 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>181</v>
@@ -4828,7 +4835,7 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
@@ -4868,16 +4875,16 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>232</v>
@@ -4947,7 +4954,7 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
@@ -4996,7 +5003,7 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>181</v>
@@ -5066,7 +5073,7 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
@@ -5103,19 +5110,19 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>167</v>
@@ -5223,7 +5230,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -5298,7 +5305,7 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
@@ -5452,19 +5459,19 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>192</v>
@@ -5574,7 +5581,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5649,7 +5656,7 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5803,19 +5810,19 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>102</v>
@@ -5885,7 +5892,7 @@
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
@@ -5925,16 +5932,16 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>181</v>
@@ -6002,7 +6009,7 @@
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
@@ -6039,19 +6046,19 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>108</v>
@@ -6119,7 +6126,7 @@
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -6159,16 +6166,16 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>181</v>
@@ -6236,7 +6243,7 @@
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -6276,16 +6283,16 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>232</v>
@@ -6355,7 +6362,7 @@
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -6404,7 +6411,7 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>181</v>
@@ -6474,7 +6481,7 @@
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -6514,16 +6521,16 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>167</v>
@@ -6629,7 +6636,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6704,7 +6711,7 @@
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
@@ -6858,19 +6865,19 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>192</v>
@@ -6980,7 +6987,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -7055,7 +7062,7 @@
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -7209,19 +7216,19 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>102</v>
@@ -7291,7 +7298,7 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -7331,16 +7338,16 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>181</v>
@@ -7408,7 +7415,7 @@
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
@@ -7445,19 +7452,19 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>108</v>
@@ -7525,7 +7532,7 @@
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
@@ -7565,16 +7572,16 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>181</v>
@@ -7642,7 +7649,7 @@
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
@@ -7682,16 +7689,16 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>232</v>
@@ -7761,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
@@ -7810,7 +7817,7 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>181</v>
@@ -7880,7 +7887,7 @@
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7917,19 +7924,19 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>167</v>
@@ -7965,7 +7972,7 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
         <v>287</v>
@@ -7995,7 +8002,7 @@
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -8035,7 +8042,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -8110,7 +8117,7 @@
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -8264,19 +8271,19 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>192</v>
@@ -8386,7 +8393,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -8461,7 +8468,7 @@
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -8615,19 +8622,19 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>102</v>
@@ -8697,7 +8704,7 @@
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8737,16 +8744,16 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>181</v>
@@ -8814,7 +8821,7 @@
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8851,19 +8858,19 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>108</v>
@@ -8931,7 +8938,7 @@
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8971,16 +8978,16 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>181</v>
@@ -9048,7 +9055,7 @@
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
@@ -9088,16 +9095,16 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>232</v>
@@ -9167,7 +9174,7 @@
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
@@ -9216,7 +9223,7 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>181</v>
@@ -9286,7 +9293,7 @@
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -9335,7 +9342,7 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>167</v>
@@ -9438,10 +9445,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -9631,7 +9638,7 @@
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
@@ -9785,19 +9792,19 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>181</v>
@@ -9865,7 +9872,7 @@
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>324</v>
@@ -9914,7 +9921,7 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>102</v>
@@ -9982,7 +9989,7 @@
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -10031,7 +10038,7 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>146</v>
@@ -10099,7 +10106,7 @@
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
@@ -10148,7 +10155,7 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>181</v>
@@ -10216,7 +10223,7 @@
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
@@ -10333,7 +10340,7 @@
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
@@ -10448,7 +10455,7 @@
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
@@ -10488,7 +10495,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10676,7 +10683,7 @@
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
@@ -10833,16 +10840,16 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>181</v>
@@ -10910,7 +10917,7 @@
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>324</v>
@@ -10959,7 +10966,7 @@
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>102</v>
@@ -11027,7 +11034,7 @@
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
@@ -11067,16 +11074,16 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>146</v>
@@ -11144,7 +11151,7 @@
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
@@ -11259,7 +11266,7 @@
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -11422,10 +11429,10 @@
         <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>108</v>
@@ -11495,7 +11502,7 @@
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
@@ -11544,7 +11551,7 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>167</v>
@@ -11614,7 +11621,7 @@
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
@@ -11654,16 +11661,16 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>102</v>
@@ -11733,7 +11740,7 @@
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
@@ -11773,16 +11780,16 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>181</v>
@@ -11850,7 +11857,7 @@
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
@@ -11899,7 +11906,7 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>411</v>
@@ -11965,7 +11972,7 @@
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
@@ -12014,7 +12021,7 @@
         <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>418</v>
@@ -12082,7 +12089,7 @@
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
@@ -12131,7 +12138,7 @@
         <v>77</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>181</v>
@@ -12199,7 +12206,7 @@
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
@@ -12241,7 +12248,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
@@ -12259,7 +12266,7 @@
         <v>428</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12342,7 +12349,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>368</v>
@@ -12431,7 +12438,7 @@
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>77</v>
@@ -12457,7 +12464,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>369</v>
@@ -12574,7 +12581,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>370</v>
@@ -12588,16 +12595,16 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>181</v>
@@ -12665,7 +12672,7 @@
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>324</v>
@@ -12691,7 +12698,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>371</v>
@@ -12714,7 +12721,7 @@
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>102</v>
@@ -12782,7 +12789,7 @@
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>77</v>
@@ -12808,7 +12815,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>372</v>
@@ -12819,19 +12826,19 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>146</v>
@@ -12899,13 +12906,13 @@
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>435</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
@@ -12925,7 +12932,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>373</v>
@@ -13014,7 +13021,7 @@
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>77</v>
@@ -13040,7 +13047,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>374</v>
@@ -13157,7 +13164,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>375</v>
@@ -13177,10 +13184,10 @@
         <v>77</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>108</v>
@@ -13250,7 +13257,7 @@
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>77</v>
@@ -13276,7 +13283,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>384</v>
@@ -13299,7 +13306,7 @@
         <v>77</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>167</v>
@@ -13369,7 +13376,7 @@
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>77</v>
@@ -13395,7 +13402,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>393</v>
@@ -13406,19 +13413,19 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>102</v>
@@ -13440,7 +13447,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>77</v>
@@ -13488,7 +13495,7 @@
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>77</v>
@@ -13514,7 +13521,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>402</v>
@@ -13525,19 +13532,19 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G98" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>181</v>
@@ -13605,7 +13612,7 @@
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>77</v>
@@ -13631,7 +13638,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>410</v>
@@ -13654,7 +13661,7 @@
         <v>77</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>411</v>
@@ -13720,7 +13727,7 @@
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>77</v>
@@ -13746,7 +13753,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>417</v>
@@ -13769,7 +13776,7 @@
         <v>77</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>418</v>
@@ -13837,7 +13844,7 @@
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>77</v>
@@ -13863,7 +13870,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>425</v>
@@ -13886,7 +13893,7 @@
         <v>77</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>181</v>
@@ -13954,7 +13961,7 @@
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>77</v>
@@ -13980,10 +13987,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13994,25 +14001,25 @@
         <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K102" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14063,42 +14070,42 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14109,25 +14116,25 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J103" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K103" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14178,42 +14185,42 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14236,13 +14243,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14293,13 +14300,13 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>77</v>
@@ -14308,13 +14315,13 @@
         <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>77</v>
@@ -14325,10 +14332,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14351,13 +14358,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14408,7 +14415,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14426,7 +14433,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -14440,10 +14447,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14454,7 +14461,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>77</v>
@@ -14466,16 +14473,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14525,13 +14532,13 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>77</v>
@@ -14540,13 +14547,13 @@
         <v>100</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>77</v>
@@ -14557,10 +14564,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14586,13 +14593,13 @@
         <v>181</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14642,13 +14649,13 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>77</v>
@@ -14657,13 +14664,13 @@
         <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>77</v>
@@ -14674,10 +14681,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14703,10 +14710,10 @@
         <v>181</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14757,13 +14764,13 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>77</v>
@@ -14775,10 +14782,10 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>77</v>
@@ -14789,21 +14796,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>77</v>
@@ -14815,13 +14822,13 @@
         <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14872,7 +14879,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14887,10 +14894,10 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -14904,10 +14911,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14993,7 +15000,7 @@
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>77</v>
@@ -15019,10 +15026,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15136,10 +15143,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15147,19 +15154,19 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>181</v>
@@ -15227,7 +15234,7 @@
         <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>324</v>
@@ -15253,10 +15260,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15276,7 +15283,7 @@
         <v>77</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
         <v>102</v>
@@ -15344,7 +15351,7 @@
         <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>77</v>
@@ -15370,10 +15377,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15393,7 +15400,7 @@
         <v>77</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
         <v>146</v>
@@ -15461,7 +15468,7 @@
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>77</v>
@@ -15487,10 +15494,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15510,7 +15517,7 @@
         <v>77</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>181</v>
@@ -15578,7 +15585,7 @@
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>77</v>
@@ -15604,10 +15611,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15615,10 +15622,10 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>77</v>
@@ -15630,13 +15637,13 @@
         <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15687,10 +15694,10 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>79</v>
@@ -15699,30 +15706,30 @@
         <v>77</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15808,7 +15815,7 @@
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>77</v>
@@ -15834,10 +15841,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15951,14 +15958,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15971,19 +15978,19 @@
         <v>77</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>137</v>
@@ -16038,7 +16045,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16070,10 +16077,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16081,31 +16088,31 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J120" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>167</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16134,10 +16141,10 @@
         <v>158</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>77</v>
@@ -16155,7 +16162,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16173,7 +16180,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>172</v>
@@ -16182,15 +16189,15 @@
         <v>77</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16276,7 +16283,7 @@
         <v>78</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>77</v>
@@ -16302,10 +16309,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16419,10 +16426,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16430,19 +16437,19 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J123" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>192</v>
@@ -16538,10 +16545,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16627,7 +16634,7 @@
         <v>78</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>77</v>
@@ -16653,10 +16660,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16770,10 +16777,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16781,19 +16788,19 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J126" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>102</v>
@@ -16863,7 +16870,7 @@
         <v>78</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>77</v>
@@ -16889,10 +16896,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16903,16 +16910,16 @@
         <v>78</v>
       </c>
       <c r="G127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J127" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>181</v>
@@ -16980,7 +16987,7 @@
         <v>78</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>77</v>
@@ -17006,10 +17013,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17017,19 +17024,19 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J128" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K128" t="s" s="2">
         <v>108</v>
@@ -17049,7 +17056,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>77</v>
@@ -17097,7 +17104,7 @@
         <v>78</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>77</v>
@@ -17123,10 +17130,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17137,16 +17144,16 @@
         <v>78</v>
       </c>
       <c r="G129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J129" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
         <v>181</v>
@@ -17214,7 +17221,7 @@
         <v>78</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>77</v>
@@ -17240,10 +17247,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17263,7 +17270,7 @@
         <v>77</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>232</v>
@@ -17333,7 +17340,7 @@
         <v>78</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>77</v>
@@ -17359,10 +17366,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17382,7 +17389,7 @@
         <v>77</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>181</v>
@@ -17452,7 +17459,7 @@
         <v>78</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>77</v>
@@ -17478,10 +17485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17489,28 +17496,28 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J132" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G132" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K132" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17561,13 +17568,13 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>77</v>
@@ -17682,7 +17689,7 @@
         <v>78</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>77</v>
@@ -17848,7 +17855,7 @@
         <v>77</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>181</v>
@@ -17916,7 +17923,7 @@
         <v>78</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>324</v>
@@ -17965,7 +17972,7 @@
         <v>77</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K136" t="s" s="2">
         <v>102</v>
@@ -18033,7 +18040,7 @@
         <v>78</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>77</v>
@@ -18070,19 +18077,19 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J137" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K137" t="s" s="2">
         <v>146</v>
@@ -18150,13 +18157,13 @@
         <v>78</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>100</v>
+        <v>551</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>77</v>
@@ -18176,10 +18183,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18265,7 +18272,7 @@
         <v>78</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>77</v>
@@ -18291,10 +18298,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18408,10 +18415,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18428,10 +18435,10 @@
         <v>77</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>108</v>
@@ -18501,7 +18508,7 @@
         <v>78</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>77</v>
@@ -18527,10 +18534,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18550,7 +18557,7 @@
         <v>77</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>167</v>
@@ -18620,7 +18627,7 @@
         <v>78</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>77</v>
@@ -18646,10 +18653,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18657,19 +18664,19 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J142" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>102</v>
@@ -18739,7 +18746,7 @@
         <v>78</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>77</v>
@@ -18765,10 +18772,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18776,19 +18783,19 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J143" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>181</v>
@@ -18856,7 +18863,7 @@
         <v>78</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>77</v>
@@ -18882,10 +18889,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18905,7 +18912,7 @@
         <v>77</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>411</v>
@@ -18971,7 +18978,7 @@
         <v>78</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>77</v>
@@ -18997,10 +19004,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19020,7 +19027,7 @@
         <v>77</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
         <v>418</v>
@@ -19088,7 +19095,7 @@
         <v>78</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>77</v>
@@ -19114,10 +19121,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19137,7 +19144,7 @@
         <v>77</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>181</v>
@@ -19205,7 +19212,7 @@
         <v>78</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>77</v>
@@ -19231,10 +19238,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19254,16 +19261,16 @@
         <v>77</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19293,10 +19300,10 @@
         <v>158</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>77</v>
@@ -19314,13 +19321,13 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>77</v>
@@ -19332,10 +19339,10 @@
         <v>77</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>77</v>
@@ -19346,10 +19353,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19357,28 +19364,28 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J148" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19408,34 +19415,34 @@
         <v>158</v>
       </c>
       <c r="Y148" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="Z148" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="AG148" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>77</v>
@@ -19447,24 +19454,24 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19490,10 +19497,10 @@
         <v>411</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19544,13 +19551,13 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>77</v>
@@ -19576,10 +19583,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19605,13 +19612,13 @@
         <v>411</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19661,7 +19668,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19676,10 +19683,10 @@
         <v>100</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
@@ -19688,7 +19695,7 @@
         <v>77</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
